--- a/config/PARAFUSOS POR ESTRUTURA.xlsx
+++ b/config/PARAFUSOS POR ESTRUTURA.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.araujo\Desktop\sistema_quantitativos\data\input\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vinicius.araujo\Desktop\sistema_quantitativos\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21C74044-527F-47F5-91CB-8A7A21F2826A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DA1568-0427-4EEC-9E01-673312076AB1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="2" xr2:uid="{40D93831-C4EA-4F94-8D0C-E4875C6CAE9F}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="32">
   <si>
     <t>N1</t>
   </si>
@@ -131,6 +131,9 @@
   </si>
   <si>
     <t>I</t>
+  </si>
+  <si>
+    <t>2TE.TR-CH</t>
   </si>
 </sst>
 </file>
@@ -1964,7 +1967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A627A873-5834-4AF1-8DE1-5159D8BB05DF}">
-  <dimension ref="A1:W112"/>
+  <dimension ref="A1:W115"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.28515625" style="1" bestFit="1" customWidth="1"/>
@@ -2491,7 +2494,7 @@
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O22" s="1">
         <v>2</v>
@@ -2527,7 +2530,7 @@
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O23" s="1">
         <v>3</v>
@@ -2564,7 +2567,7 @@
       </c>
       <c r="G25" s="2"/>
       <c r="H25" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N25" s="1">
         <v>2</v>
@@ -2600,7 +2603,7 @@
       </c>
       <c r="G26" s="2"/>
       <c r="H26" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O26" s="1">
         <v>3</v>
@@ -2747,7 +2750,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="3"/>
@@ -2757,7 +2760,7 @@
       <c r="G33" s="3"/>
       <c r="H33" s="3"/>
     </row>
-    <row r="34" spans="1:22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>23</v>
       </c>
@@ -2768,7 +2771,7 @@
         <v>15</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E34" s="2" t="s">
         <v>7</v>
@@ -2778,20 +2781,20 @@
       </c>
       <c r="G34" s="2"/>
       <c r="H34" s="2"/>
-      <c r="N34" s="1">
-        <v>2</v>
-      </c>
       <c r="O34" s="1">
         <v>2</v>
       </c>
-      <c r="Q34" s="1">
-        <v>4</v>
+      <c r="P34" s="1">
+        <v>2</v>
       </c>
       <c r="R34" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="S34" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>23</v>
       </c>
@@ -2802,7 +2805,7 @@
         <v>15</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E35" s="2" t="s">
         <v>11</v>
@@ -2813,10 +2816,13 @@
       <c r="G35" s="2"/>
       <c r="H35" s="2"/>
       <c r="O35" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="P35" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -2826,18 +2832,18 @@
       <c r="G36" s="3"/>
       <c r="H36" s="3"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B37" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C37" s="2">
         <v>15</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E37" s="2" t="s">
         <v>7</v>
@@ -2847,28 +2853,31 @@
       </c>
       <c r="G37" s="2"/>
       <c r="H37" s="2"/>
-      <c r="P37" s="1">
-        <v>4</v>
-      </c>
-      <c r="S37" s="1">
-        <v>4</v>
-      </c>
-      <c r="T37" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="N37" s="1">
+        <v>2</v>
+      </c>
+      <c r="O37" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q37" s="1">
+        <v>4</v>
+      </c>
+      <c r="R37" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B38" s="2">
-        <v>1500</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="2">
         <v>15</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E38" s="2" t="s">
         <v>11</v>
@@ -2878,14 +2887,11 @@
       </c>
       <c r="G38" s="2"/>
       <c r="H38" s="2"/>
-      <c r="P38" s="1">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="O38" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -2895,18 +2901,18 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B40" s="2">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="C40" s="2">
         <v>15</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E40" s="2" t="s">
         <v>7</v>
@@ -2916,28 +2922,28 @@
       </c>
       <c r="G40" s="2"/>
       <c r="H40" s="2"/>
-      <c r="O40" s="1">
-        <v>4</v>
-      </c>
-      <c r="R40" s="1">
+      <c r="P40" s="1">
         <v>4</v>
       </c>
       <c r="S40" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T40" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B41" s="2">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="C41" s="2">
         <v>15</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E41" s="2" t="s">
         <v>11</v>
@@ -2947,14 +2953,14 @@
       </c>
       <c r="G41" s="2"/>
       <c r="H41" s="2"/>
-      <c r="O41" s="1">
-        <v>3</v>
-      </c>
       <c r="P41" s="1">
         <v>3</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Q41" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -2964,18 +2970,18 @@
       <c r="G42" s="3"/>
       <c r="H42" s="3"/>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B43" s="2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="C43" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>7</v>
@@ -2984,10 +2990,8 @@
         <v>50</v>
       </c>
       <c r="G43" s="2"/>
-      <c r="H43" s="2">
-        <v>1</v>
-      </c>
-      <c r="P43" s="1">
+      <c r="H43" s="2"/>
+      <c r="O43" s="1">
         <v>4</v>
       </c>
       <c r="R43" s="1">
@@ -2996,22 +3000,19 @@
       <c r="S43" s="1">
         <v>4</v>
       </c>
-      <c r="T43" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B44" s="2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="C44" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>11</v>
@@ -3020,17 +3021,15 @@
         <v>50</v>
       </c>
       <c r="G44" s="2"/>
-      <c r="H44" s="2">
-        <v>1</v>
+      <c r="H44" s="2"/>
+      <c r="O44" s="1">
+        <v>3</v>
       </c>
       <c r="P44" s="1">
         <v>3</v>
       </c>
-      <c r="Q44" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -3040,15 +3039,15 @@
       <c r="G45" s="3"/>
       <c r="H45" s="3"/>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B46" s="2">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="C46" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>9</v>
@@ -3061,33 +3060,30 @@
       </c>
       <c r="G46" s="2"/>
       <c r="H46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="P46" s="1">
-        <v>2</v>
-      </c>
-      <c r="Q46" s="1">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="R46" s="1">
+        <v>4</v>
       </c>
       <c r="S46" s="1">
         <v>4</v>
       </c>
-      <c r="U46" s="1">
-        <v>4</v>
-      </c>
-      <c r="V46" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="T46" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>23</v>
       </c>
       <c r="B47" s="2">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="C47" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>9</v>
@@ -3100,16 +3096,16 @@
       </c>
       <c r="G47" s="2"/>
       <c r="H47" s="2">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="P47" s="1">
+        <v>3</v>
       </c>
       <c r="Q47" s="1">
         <v>3</v>
       </c>
-      <c r="R47" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -3119,15 +3115,15 @@
       <c r="G48" s="3"/>
       <c r="H48" s="3"/>
     </row>
-    <row r="49" spans="1:20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B49" s="2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="C49" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>9</v>
@@ -3139,29 +3135,34 @@
         <v>50</v>
       </c>
       <c r="G49" s="2"/>
-      <c r="H49" s="2"/>
+      <c r="H49" s="2">
+        <v>2</v>
+      </c>
       <c r="P49" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q49" s="1">
-        <v>3</v>
-      </c>
-      <c r="R49" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="S49" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="50" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="U49" s="1">
+        <v>4</v>
+      </c>
+      <c r="V49" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B50" s="2">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="C50" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>9</v>
@@ -3173,12 +3174,17 @@
         <v>50</v>
       </c>
       <c r="G50" s="2"/>
-      <c r="H50" s="2"/>
-      <c r="P50" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="51" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="H50" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q50" s="1">
+        <v>3</v>
+      </c>
+      <c r="R50" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -3188,7 +3194,7 @@
       <c r="G51" s="3"/>
       <c r="H51" s="3"/>
     </row>
-    <row r="52" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>24</v>
       </c>
@@ -3196,7 +3202,7 @@
         <v>1500</v>
       </c>
       <c r="C52" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>9</v>
@@ -3215,14 +3221,14 @@
       <c r="Q52" s="1">
         <v>3</v>
       </c>
+      <c r="R52" s="1">
+        <v>4</v>
+      </c>
       <c r="S52" s="1">
         <v>4</v>
       </c>
-      <c r="T52" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="53" spans="1:20" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>24</v>
       </c>
@@ -3230,7 +3236,7 @@
         <v>1500</v>
       </c>
       <c r="C53" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>9</v>
@@ -3247,7 +3253,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -3257,7 +3263,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>24</v>
       </c>
@@ -3268,7 +3274,7 @@
         <v>15</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>7</v>
@@ -3278,17 +3284,20 @@
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2"/>
-      <c r="O55" s="1">
-        <v>7</v>
-      </c>
-      <c r="R55" s="1">
-        <v>4</v>
+      <c r="P55" s="1">
+        <v>4</v>
+      </c>
+      <c r="Q55" s="1">
+        <v>3</v>
       </c>
       <c r="S55" s="1">
         <v>4</v>
       </c>
-    </row>
-    <row r="56" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="T55" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>24</v>
       </c>
@@ -3299,7 +3308,7 @@
         <v>15</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>11</v>
@@ -3309,11 +3318,11 @@
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2"/>
-      <c r="O56" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="57" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="P56" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -3323,27 +3332,63 @@
       <c r="G57" s="3"/>
       <c r="H57" s="3"/>
     </row>
-    <row r="58" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A58" s="3"/>
-      <c r="B58" s="3"/>
-      <c r="C58" s="3"/>
-      <c r="D58" s="3"/>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="G58" s="3"/>
-      <c r="H58" s="3"/>
-    </row>
-    <row r="59" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="D59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="G59" s="3"/>
-      <c r="H59" s="3"/>
-    </row>
-    <row r="60" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B58" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C58" s="2">
+        <v>15</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F58" s="2">
+        <v>50</v>
+      </c>
+      <c r="G58" s="2"/>
+      <c r="H58" s="2"/>
+      <c r="O58" s="1">
+        <v>7</v>
+      </c>
+      <c r="R58" s="1">
+        <v>4</v>
+      </c>
+      <c r="S58" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B59" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C59" s="2">
+        <v>15</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F59" s="2">
+        <v>50</v>
+      </c>
+      <c r="G59" s="2"/>
+      <c r="H59" s="2"/>
+      <c r="O59" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -3353,7 +3398,7 @@
       <c r="G60" s="3"/>
       <c r="H60" s="3"/>
     </row>
-    <row r="61" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -3363,7 +3408,7 @@
       <c r="G61" s="3"/>
       <c r="H61" s="3"/>
     </row>
-    <row r="62" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -3373,7 +3418,7 @@
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -3383,7 +3428,7 @@
       <c r="G63" s="3"/>
       <c r="H63" s="3"/>
     </row>
-    <row r="64" spans="1:20" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -3872,6 +3917,36 @@
       <c r="F112" s="3"/>
       <c r="G112" s="3"/>
       <c r="H112" s="3"/>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="3"/>
+      <c r="B113" s="3"/>
+      <c r="C113" s="3"/>
+      <c r="D113" s="3"/>
+      <c r="E113" s="3"/>
+      <c r="F113" s="3"/>
+      <c r="G113" s="3"/>
+      <c r="H113" s="3"/>
+    </row>
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A114" s="3"/>
+      <c r="B114" s="3"/>
+      <c r="C114" s="3"/>
+      <c r="D114" s="3"/>
+      <c r="E114" s="3"/>
+      <c r="F114" s="3"/>
+      <c r="G114" s="3"/>
+      <c r="H114" s="3"/>
+    </row>
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A115" s="3"/>
+      <c r="B115" s="3"/>
+      <c r="C115" s="3"/>
+      <c r="D115" s="3"/>
+      <c r="E115" s="3"/>
+      <c r="F115" s="3"/>
+      <c r="G115" s="3"/>
+      <c r="H115" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
@@ -5076,7 +5151,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="49" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>28</v>
       </c>
@@ -5104,7 +5179,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -5114,7 +5189,7 @@
       <c r="G50" s="3"/>
       <c r="H50" s="3"/>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>28</v>
       </c>
@@ -5139,7 +5214,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>28</v>
       </c>
@@ -5164,7 +5239,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>28</v>
       </c>
@@ -5192,7 +5267,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -5202,7 +5277,7 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>29</v>
       </c>
@@ -5223,7 +5298,7 @@
       </c>
       <c r="G55" s="2"/>
       <c r="H55" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K55" s="1">
         <v>2</v>
@@ -5241,7 +5316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>29</v>
       </c>
@@ -5262,13 +5337,13 @@
       </c>
       <c r="G56" s="2"/>
       <c r="H56" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q56" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>29</v>
       </c>
@@ -5289,7 +5364,7 @@
       </c>
       <c r="G57" s="2"/>
       <c r="H57" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M57" s="1">
         <v>1</v>
@@ -5298,7 +5373,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -5308,7 +5383,7 @@
       <c r="G58" s="3"/>
       <c r="H58" s="3"/>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>29</v>
       </c>
@@ -5329,7 +5404,7 @@
       </c>
       <c r="G59" s="2"/>
       <c r="H59" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N59" s="1">
         <v>2</v>
@@ -5347,7 +5422,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>29</v>
       </c>
@@ -5368,13 +5443,13 @@
       </c>
       <c r="G60" s="2"/>
       <c r="H60" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q60" s="1">
         <v>3</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>29</v>
       </c>
@@ -5395,7 +5470,7 @@
       </c>
       <c r="G61" s="2"/>
       <c r="H61" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M61" s="1">
         <v>1</v>
@@ -5404,7 +5479,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -5414,37 +5489,112 @@
       <c r="G62" s="3"/>
       <c r="H62" s="3"/>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A63" s="3"/>
-      <c r="B63" s="3"/>
-      <c r="C63" s="3"/>
-      <c r="D63" s="3"/>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="G63" s="3"/>
-      <c r="H63" s="3"/>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
-      <c r="D64" s="3"/>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="G64" s="3"/>
-      <c r="H64" s="3"/>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="3"/>
-      <c r="B65" s="3"/>
-      <c r="C65" s="3"/>
-      <c r="D65" s="3"/>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="G65" s="3"/>
-      <c r="H65" s="3"/>
-    </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A63" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B63" s="2">
+        <v>3000</v>
+      </c>
+      <c r="C63" s="2">
+        <v>19</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F63" s="2">
+        <v>50</v>
+      </c>
+      <c r="G63" s="2"/>
+      <c r="H63" s="2">
+        <v>2</v>
+      </c>
+      <c r="N63" s="1">
+        <v>2</v>
+      </c>
+      <c r="O63" s="1">
+        <v>2</v>
+      </c>
+      <c r="T63" s="1">
+        <v>4</v>
+      </c>
+      <c r="V63" s="1">
+        <v>4</v>
+      </c>
+      <c r="W63" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A64" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B64" s="2">
+        <v>3000</v>
+      </c>
+      <c r="C64" s="2">
+        <v>19</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F64" s="2">
+        <v>70</v>
+      </c>
+      <c r="G64" s="2"/>
+      <c r="H64" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q64" s="1">
+        <v>3</v>
+      </c>
+      <c r="S64" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A65" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B65" s="2">
+        <v>3000</v>
+      </c>
+      <c r="C65" s="2">
+        <v>19</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F65" s="2">
+        <v>70</v>
+      </c>
+      <c r="G65" s="2"/>
+      <c r="H65" s="2">
+        <v>2</v>
+      </c>
+      <c r="M65" s="1">
+        <v>1</v>
+      </c>
+      <c r="N65" s="1">
+        <v>1</v>
+      </c>
+      <c r="R65" s="1">
+        <v>2</v>
+      </c>
+      <c r="S65" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -5454,37 +5604,115 @@
       <c r="G66" s="3"/>
       <c r="H66" s="3"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="3"/>
-      <c r="B67" s="3"/>
-      <c r="C67" s="3"/>
-      <c r="D67" s="3"/>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="G67" s="3"/>
-      <c r="H67" s="3"/>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="3"/>
-      <c r="B68" s="3"/>
-      <c r="C68" s="3"/>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="G68" s="3"/>
-      <c r="H68" s="3"/>
-    </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="3"/>
-      <c r="B69" s="3"/>
-      <c r="C69" s="3"/>
-      <c r="D69" s="3"/>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="G69" s="3"/>
-      <c r="H69" s="3"/>
-    </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B67" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C67" s="2">
+        <v>20</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F67" s="2">
+        <v>50</v>
+      </c>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2">
+        <v>4</v>
+      </c>
+      <c r="K67" s="1">
+        <v>2</v>
+      </c>
+      <c r="M67" s="1">
+        <v>2</v>
+      </c>
+      <c r="R67" s="1">
+        <v>4</v>
+      </c>
+      <c r="S67" s="1">
+        <v>4</v>
+      </c>
+      <c r="T67" s="1">
+        <v>4</v>
+      </c>
+      <c r="U67" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A68" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B68" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C68" s="2">
+        <v>20</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="F68" s="2">
+        <v>70</v>
+      </c>
+      <c r="G68" s="2"/>
+      <c r="H68" s="2">
+        <v>4</v>
+      </c>
+      <c r="O68" s="1">
+        <v>3</v>
+      </c>
+      <c r="Q68" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A69" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B69" s="2">
+        <v>1500</v>
+      </c>
+      <c r="C69" s="2">
+        <v>20</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="F69" s="2">
+        <v>70</v>
+      </c>
+      <c r="G69" s="2"/>
+      <c r="H69" s="2">
+        <v>4</v>
+      </c>
+      <c r="K69" s="1">
+        <v>1</v>
+      </c>
+      <c r="M69" s="1">
+        <v>1</v>
+      </c>
+      <c r="P69" s="1">
+        <v>2</v>
+      </c>
+      <c r="Q69" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -5494,7 +5722,7 @@
       <c r="G70" s="3"/>
       <c r="H70" s="3"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -5504,7 +5732,7 @@
       <c r="G71" s="3"/>
       <c r="H71" s="3"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -5514,7 +5742,7 @@
       <c r="G72" s="3"/>
       <c r="H72" s="3"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -5524,7 +5752,7 @@
       <c r="G73" s="3"/>
       <c r="H73" s="3"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -5534,7 +5762,7 @@
       <c r="G74" s="3"/>
       <c r="H74" s="3"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -5544,7 +5772,7 @@
       <c r="G75" s="3"/>
       <c r="H75" s="3"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -5554,7 +5782,7 @@
       <c r="G76" s="3"/>
       <c r="H76" s="3"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -5564,7 +5792,7 @@
       <c r="G77" s="3"/>
       <c r="H77" s="3"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -5574,7 +5802,7 @@
       <c r="G78" s="3"/>
       <c r="H78" s="3"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -5584,7 +5812,7 @@
       <c r="G79" s="3"/>
       <c r="H79" s="3"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
